--- a/docs/总题库包含出现题库名.xlsx
+++ b/docs/总题库包含出现题库名.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Hamwiki\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E2E7960-9699-4071-9207-FAA89343F5DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B72C5480-06EE-489B-95D5-B6930FC268F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22600,176 +22600,176 @@
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+      <c r="A30" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D30" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E30" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="F30" t="s">
+      <c r="F30" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="G30" t="s">
+      <c r="G30" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="H30" t="s">
+      <c r="H30" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="I30" t="s">
+      <c r="I30" s="1" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+      <c r="A31" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D31" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="E31" t="s">
-        <v>5</v>
-      </c>
-      <c r="F31" t="s">
+      <c r="E31" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F31" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="G31" t="s">
+      <c r="G31" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="H31" t="s">
+      <c r="H31" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="I31" t="s">
+      <c r="I31" s="1" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="A32" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D32" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E32" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F32" t="s">
+      <c r="F32" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="G32" t="s">
+      <c r="G32" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="H32" t="s">
+      <c r="H32" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="I32" t="s">
+      <c r="I32" s="1" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+      <c r="A33" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D33" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E33" t="s">
+      <c r="E33" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="F33" t="s">
+      <c r="F33" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="G33" t="s">
+      <c r="G33" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="H33" t="s">
+      <c r="H33" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="I33" t="s">
+      <c r="I33" s="1" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+      <c r="A34" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D34" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="E34" t="s">
-        <v>5</v>
-      </c>
-      <c r="F34" t="s">
+      <c r="E34" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F34" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="G34" t="s">
+      <c r="G34" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="H34" t="s">
+      <c r="H34" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="I34" t="s">
+      <c r="I34" s="1" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+      <c r="A35" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D35" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="E35" t="s">
-        <v>9</v>
-      </c>
-      <c r="F35" t="s">
+      <c r="E35" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F35" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="G35" t="s">
+      <c r="G35" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="H35" t="s">
+      <c r="H35" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="I35" t="s">
+      <c r="I35" s="1" t="s">
         <v>200</v>
       </c>
     </row>

--- a/docs/总题库包含出现题库名.xlsx
+++ b/docs/总题库包含出现题库名.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Hamwiki\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A8DB95B-840B-45CD-AB54-DA26D0F68F27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CCA03C0-29B8-45C3-AC4D-8A0DE34674E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22832,234 +22832,234 @@
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+      <c r="A38" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D38" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="E38" t="s">
-        <v>5</v>
-      </c>
-      <c r="F38" t="s">
+      <c r="E38" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F38" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="G38" t="s">
+      <c r="G38" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="H38" t="s">
+      <c r="H38" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="I38" t="s">
+      <c r="I38" s="1" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+      <c r="A39" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D39" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="E39" t="s">
-        <v>5</v>
-      </c>
-      <c r="F39" t="s">
+      <c r="E39" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F39" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="G39" t="s">
+      <c r="G39" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="H39" t="s">
+      <c r="H39" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="I39" t="s">
+      <c r="I39" s="1" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+      <c r="A40" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D40" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="E40" t="s">
-        <v>5</v>
-      </c>
-      <c r="F40" t="s">
+      <c r="E40" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F40" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="G40" t="s">
+      <c r="G40" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="H40" t="s">
+      <c r="H40" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="I40" t="s">
+      <c r="I40" s="1" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+      <c r="A41" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C41" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D41" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="E41" t="s">
-        <v>9</v>
-      </c>
-      <c r="F41" t="s">
+      <c r="E41" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F41" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="G41" t="s">
+      <c r="G41" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="H41" t="s">
+      <c r="H41" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="I41" t="s">
+      <c r="I41" s="1" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>9</v>
-      </c>
-      <c r="B42" t="s">
+      <c r="A42" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C42" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="D42" t="s">
+      <c r="D42" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="E42" t="s">
-        <v>5</v>
-      </c>
-      <c r="F42" t="s">
+      <c r="E42" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F42" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="G42" t="s">
+      <c r="G42" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="H42" t="s">
+      <c r="H42" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="I42" t="s">
+      <c r="I42" s="1" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>9</v>
-      </c>
-      <c r="B43" t="s">
+      <c r="A43" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B43" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C43" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D43" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="E43" t="s">
-        <v>5</v>
-      </c>
-      <c r="F43" t="s">
+      <c r="E43" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F43" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="G43" t="s">
+      <c r="G43" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="H43" t="s">
+      <c r="H43" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="I43" t="s">
+      <c r="I43" s="1" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>9</v>
-      </c>
-      <c r="B44" t="s">
+      <c r="A44" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C44" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D44" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="E44" t="s">
-        <v>5</v>
-      </c>
-      <c r="F44" t="s">
+      <c r="E44" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="G44" t="s">
+      <c r="G44" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="H44" t="s">
+      <c r="H44" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="I44" t="s">
+      <c r="I44" s="1" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>9</v>
-      </c>
-      <c r="B45" t="s">
+      <c r="A45" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C45" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="D45" t="s">
+      <c r="D45" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="E45" t="s">
+      <c r="E45" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F45" t="s">
+      <c r="F45" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="G45" t="s">
+      <c r="G45" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="H45" t="s">
+      <c r="H45" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="I45" t="s">
+      <c r="I45" s="1" t="s">
         <v>254</v>
       </c>
     </row>

--- a/docs/总题库包含出现题库名.xlsx
+++ b/docs/总题库包含出现题库名.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Hamwiki\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CCA03C0-29B8-45C3-AC4D-8A0DE34674E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA8F98DA-2F5A-4BAE-8412-3118B0B7B8D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23064,176 +23064,176 @@
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
+      <c r="A46" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C46" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D46" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="E46" t="s">
+      <c r="E46" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F46" t="s">
+      <c r="F46" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="G46" t="s">
+      <c r="G46" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="H46" t="s">
+      <c r="H46" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="I46" t="s">
+      <c r="I46" s="1" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
+      <c r="A47" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C47" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="D47" t="s">
+      <c r="D47" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="E47" t="s">
+      <c r="E47" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F47" t="s">
+      <c r="F47" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="G47" t="s">
+      <c r="G47" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="H47" t="s">
+      <c r="H47" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="I47" t="s">
+      <c r="I47" s="1" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>9</v>
-      </c>
-      <c r="B48" t="s">
+      <c r="A48" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C48" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D48" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="E48" t="s">
+      <c r="E48" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="F48" t="s">
+      <c r="F48" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="G48" t="s">
+      <c r="G48" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="H48" t="s">
+      <c r="H48" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="I48" t="s">
+      <c r="I48" s="1" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>9</v>
-      </c>
-      <c r="B49" t="s">
+      <c r="A49" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C49" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D49" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="E49" t="s">
+      <c r="E49" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="F49" t="s">
+      <c r="F49" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="G49" t="s">
+      <c r="G49" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="H49" t="s">
+      <c r="H49" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="I49" t="s">
+      <c r="I49" s="1" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>9</v>
-      </c>
-      <c r="B50" t="s">
+      <c r="A50" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C50" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D50" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="E50" t="s">
+      <c r="E50" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F50" t="s">
+      <c r="F50" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="G50" t="s">
+      <c r="G50" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="H50" t="s">
+      <c r="H50" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="I50" t="s">
+      <c r="I50" s="1" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>9</v>
-      </c>
-      <c r="B51" t="s">
+      <c r="A51" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C51" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="D51" t="s">
+      <c r="D51" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="E51" t="s">
+      <c r="E51" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="F51" t="s">
+      <c r="F51" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="G51" t="s">
+      <c r="G51" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="H51" t="s">
+      <c r="H51" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="I51" t="s">
+      <c r="I51" s="1" t="s">
         <v>288</v>
       </c>
     </row>

--- a/docs/总题库包含出现题库名.xlsx
+++ b/docs/总题库包含出现题库名.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Hamwiki\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{557E85E0-4A31-4C08-9625-4261D2587BAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6308E1DC-F8DC-4F9D-A00B-5363F9BD7C71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24086,205 +24086,205 @@
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
+      <c r="A81" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B81" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="C81" t="s">
+      <c r="C81" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="D81" t="s">
+      <c r="D81" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="E81" t="s">
+      <c r="E81" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F81" t="s">
+      <c r="F81" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="G81" t="s">
+      <c r="G81" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="H81" t="s">
+      <c r="H81" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="I81" t="s">
+      <c r="I81" s="1" t="s">
         <v>448</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
+      <c r="A82" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B82" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="C82" t="s">
+      <c r="C82" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="D82" t="s">
+      <c r="D82" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="E82" t="s">
+      <c r="E82" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="F82" t="s">
+      <c r="F82" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="G82" t="s">
+      <c r="G82" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="H82" t="s">
+      <c r="H82" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="I82" t="s">
+      <c r="I82" s="1" t="s">
         <v>454</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
+      <c r="A83" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B83" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="C83" t="s">
+      <c r="C83" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="D83" t="s">
+      <c r="D83" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="E83" t="s">
-        <v>9</v>
-      </c>
-      <c r="F83" t="s">
+      <c r="E83" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F83" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="G83" t="s">
+      <c r="G83" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="H83" t="s">
+      <c r="H83" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="I83" t="s">
+      <c r="I83" s="1" t="s">
         <v>460</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
+      <c r="A84" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B84" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="C84" t="s">
+      <c r="C84" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="D84" t="s">
+      <c r="D84" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="E84" t="s">
-        <v>9</v>
-      </c>
-      <c r="F84" t="s">
+      <c r="E84" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F84" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="G84" t="s">
+      <c r="G84" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="H84" t="s">
+      <c r="H84" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="I84" t="s">
+      <c r="I84" s="1" t="s">
         <v>466</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
+      <c r="A85" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B85" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="C85" t="s">
+      <c r="C85" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="D85" t="s">
+      <c r="D85" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="E85" t="s">
-        <v>9</v>
-      </c>
-      <c r="F85" t="s">
+      <c r="E85" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F85" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="G85" t="s">
+      <c r="G85" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="H85" t="s">
+      <c r="H85" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="I85" t="s">
+      <c r="I85" s="1" t="s">
         <v>472</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
+      <c r="A86" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B86" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="C86" t="s">
+      <c r="C86" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="D86" t="s">
+      <c r="D86" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="E86" t="s">
-        <v>5</v>
-      </c>
-      <c r="F86" t="s">
+      <c r="E86" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F86" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="G86" t="s">
+      <c r="G86" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="H86" t="s">
+      <c r="H86" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="I86" t="s">
+      <c r="I86" s="1" t="s">
         <v>478</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
+      <c r="A87" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B87" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="C87" t="s">
+      <c r="C87" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="D87" t="s">
+      <c r="D87" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="E87" t="s">
-        <v>5</v>
-      </c>
-      <c r="F87" t="s">
+      <c r="E87" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F87" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="G87" t="s">
+      <c r="G87" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="H87" t="s">
+      <c r="H87" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="I87" t="s">
+      <c r="I87" s="1" t="s">
         <v>484</v>
       </c>
     </row>

--- a/docs/总题库包含出现题库名.xlsx
+++ b/docs/总题库包含出现题库名.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Hamwiki\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6308E1DC-F8DC-4F9D-A00B-5363F9BD7C71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E1FEBFB-2B80-4B1C-8A25-ED7FE725584A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24289,118 +24289,118 @@
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
+      <c r="A88" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B88" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="C88" t="s">
+      <c r="C88" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="D88" t="s">
+      <c r="D88" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="E88" t="s">
-        <v>9</v>
-      </c>
-      <c r="F88" t="s">
+      <c r="E88" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F88" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="G88" t="s">
+      <c r="G88" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="H88" t="s">
+      <c r="H88" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="I88" t="s">
+      <c r="I88" s="1" t="s">
         <v>490</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
+      <c r="A89" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B89" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="C89" t="s">
+      <c r="C89" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="D89" t="s">
+      <c r="D89" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="E89" t="s">
+      <c r="E89" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="F89" t="s">
+      <c r="F89" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="G89" t="s">
+      <c r="G89" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="H89" t="s">
+      <c r="H89" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="I89" t="s">
+      <c r="I89" s="1" t="s">
         <v>496</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
+      <c r="A90" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B90" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="C90" t="s">
+      <c r="C90" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="D90" t="s">
+      <c r="D90" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="E90" t="s">
-        <v>5</v>
-      </c>
-      <c r="F90" t="s">
+      <c r="E90" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F90" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="G90" t="s">
+      <c r="G90" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="H90" t="s">
+      <c r="H90" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="I90" t="s">
+      <c r="I90" s="1" t="s">
         <v>502</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
+      <c r="A91" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B91" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="C91" t="s">
+      <c r="C91" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="D91" t="s">
+      <c r="D91" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="E91" t="s">
-        <v>5</v>
-      </c>
-      <c r="F91" t="s">
+      <c r="E91" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F91" s="1" t="s">
         <v>505</v>
       </c>
-      <c r="G91" t="s">
+      <c r="G91" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="H91" t="s">
+      <c r="H91" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="I91" t="s">
+      <c r="I91" s="1" t="s">
         <v>508</v>
       </c>
     </row>

--- a/docs/总题库包含出现题库名.xlsx
+++ b/docs/总题库包含出现题库名.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Hamwiki\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E1FEBFB-2B80-4B1C-8A25-ED7FE725584A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AE19FE3-06B2-43D1-BEDB-F10C77EBED34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24405,292 +24405,292 @@
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>5</v>
-      </c>
-      <c r="B92" t="s">
+      <c r="A92" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="C92" t="s">
+      <c r="C92" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="D92" t="s">
+      <c r="D92" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="E92" t="s">
-        <v>5</v>
-      </c>
-      <c r="F92" t="s">
+      <c r="E92" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F92" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="G92" t="s">
+      <c r="G92" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="H92" t="s">
+      <c r="H92" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="I92" t="s">
+      <c r="I92" s="1" t="s">
         <v>515</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>5</v>
-      </c>
-      <c r="B93" t="s">
+      <c r="A93" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="C93" t="s">
+      <c r="C93" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="D93" t="s">
+      <c r="D93" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="E93" t="s">
-        <v>9</v>
-      </c>
-      <c r="F93" t="s">
+      <c r="E93" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F93" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="G93" t="s">
+      <c r="G93" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="H93" t="s">
+      <c r="H93" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="I93" t="s">
+      <c r="I93" s="1" t="s">
         <v>520</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>5</v>
-      </c>
-      <c r="B94" t="s">
+      <c r="A94" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="C94" t="s">
+      <c r="C94" s="1" t="s">
         <v>521</v>
       </c>
-      <c r="D94" t="s">
+      <c r="D94" s="1" t="s">
         <v>522</v>
       </c>
-      <c r="E94" t="s">
+      <c r="E94" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="F94" t="s">
+      <c r="F94" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="G94" t="s">
+      <c r="G94" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="H94" t="s">
+      <c r="H94" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="I94" t="s">
+      <c r="I94" s="1" t="s">
         <v>525</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>5</v>
-      </c>
-      <c r="B95" t="s">
+      <c r="A95" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B95" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="C95" t="s">
+      <c r="C95" s="1" t="s">
         <v>526</v>
       </c>
-      <c r="D95" t="s">
+      <c r="D95" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="E95" t="s">
-        <v>9</v>
-      </c>
-      <c r="F95" t="s">
+      <c r="E95" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F95" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="G95" t="s">
+      <c r="G95" s="1" t="s">
         <v>528</v>
       </c>
-      <c r="H95" t="s">
+      <c r="H95" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="I95" t="s">
+      <c r="I95" s="1" t="s">
         <v>530</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>5</v>
-      </c>
-      <c r="B96" t="s">
+      <c r="A96" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B96" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="C96" t="s">
+      <c r="C96" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="D96" t="s">
+      <c r="D96" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="E96" t="s">
-        <v>9</v>
-      </c>
-      <c r="F96" t="s">
+      <c r="E96" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F96" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G96" t="s">
+      <c r="G96" s="1" t="s">
         <v>534</v>
       </c>
-      <c r="H96" t="s">
+      <c r="H96" s="1" t="s">
         <v>535</v>
       </c>
-      <c r="I96" t="s">
+      <c r="I96" s="1" t="s">
         <v>536</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
-        <v>5</v>
-      </c>
-      <c r="B97" t="s">
+      <c r="A97" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B97" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="C97" t="s">
+      <c r="C97" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="D97" t="s">
+      <c r="D97" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="E97" t="s">
-        <v>9</v>
-      </c>
-      <c r="F97" t="s">
+      <c r="E97" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F97" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="G97" t="s">
+      <c r="G97" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="H97" t="s">
+      <c r="H97" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="I97" t="s">
+      <c r="I97" s="1" t="s">
         <v>542</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>5</v>
-      </c>
-      <c r="B98" t="s">
+      <c r="A98" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="C98" t="s">
+      <c r="C98" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="D98" t="s">
+      <c r="D98" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="E98" t="s">
+      <c r="E98" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="F98" t="s">
+      <c r="F98" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="G98" t="s">
+      <c r="G98" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="H98" t="s">
+      <c r="H98" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="I98" t="s">
+      <c r="I98" s="1" t="s">
         <v>530</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
-        <v>5</v>
-      </c>
-      <c r="B99" t="s">
+      <c r="A99" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="C99" t="s">
+      <c r="C99" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="D99" t="s">
+      <c r="D99" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="E99" t="s">
+      <c r="E99" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="F99" t="s">
+      <c r="F99" s="1" t="s">
         <v>542</v>
       </c>
-      <c r="G99" t="s">
+      <c r="G99" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="H99" t="s">
+      <c r="H99" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="I99" t="s">
+      <c r="I99" s="1" t="s">
         <v>550</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
-        <v>5</v>
-      </c>
-      <c r="B100" t="s">
+      <c r="A100" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="C100" t="s">
+      <c r="C100" s="1" t="s">
         <v>551</v>
       </c>
-      <c r="D100" t="s">
+      <c r="D100" s="1" t="s">
         <v>552</v>
       </c>
-      <c r="E100" t="s">
+      <c r="E100" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="F100" t="s">
+      <c r="F100" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="G100" t="s">
+      <c r="G100" s="1" t="s">
         <v>554</v>
       </c>
-      <c r="H100" t="s">
+      <c r="H100" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="I100" t="s">
+      <c r="I100" s="1" t="s">
         <v>556</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
-        <v>5</v>
-      </c>
-      <c r="B101" t="s">
+      <c r="A101" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="C101" t="s">
+      <c r="C101" s="1" t="s">
         <v>557</v>
       </c>
-      <c r="D101" t="s">
+      <c r="D101" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="E101" t="s">
+      <c r="E101" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F101" t="s">
+      <c r="F101" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="G101" t="s">
+      <c r="G101" s="1" t="s">
         <v>560</v>
       </c>
-      <c r="H101" t="s">
+      <c r="H101" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="I101" t="s">
+      <c r="I101" s="1" t="s">
         <v>548</v>
       </c>
     </row>
